--- a/teacher_forms/021_get_logarithm_log_form--teacher_forms.xlsx
+++ b/teacher_forms/021_get_logarithm_log_form--teacher_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,18 +520,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>base_number</t>
+          <t>base_number_input</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>base_number</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is the base number?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Enter the base number</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,18 +547,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>exponent_number</t>
+          <t>exponent_number_input</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>exponent_number</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What is the exponent number?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Enter the exponent number</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +574,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>logarithm_result</t>
+          <t>logarithm_result_text</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>logarithm_result</t>
+          <t>What is the result of the logarithm?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,12 +597,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>logarithm_base</t>
+          <t>base_select_one</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>logarithm_base</t>
+          <t>What base are you using?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,23 +615,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>logarithm_result</t>
+          <t>logarithm_base_select_one</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>logarithm_result</t>
+          <t>What is the logarithm base?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,41 +643,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>logarithm_result</t>
+          <t>is_result_correct</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>logarithm_result</t>
+          <t>Is the result correct?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>logarithm_result</t>
+          <t>logarithm_result_note</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>logarithm_result</t>
+          <t>Logarithm Result Note</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,18 +689,110 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>logarithm_result</t>
+          <t>base_logarithm_input</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>logarithm_result</t>
+          <t>What is the base of the logarithm?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>exponentiation_input</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>What is the result of the exponentiation?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>logarithm_result_text_2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Logarithm Result Text 2</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>exponentiation_input_2</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Exponentiation Input 2</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>logarithm_result_text_3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Logarithm Result Text 3</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -707,10 +807,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
   </cols>
@@ -735,7 +835,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>logarithm_base_choices</t>
+          <t>base_select_one_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -752,7 +852,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>logarithm_base_choices</t>
+          <t>base_select_one_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -769,7 +869,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>logarithm_base_choices</t>
+          <t>base_select_one_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -779,7 +879,58 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>logarithm_base_select_one_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>logarithm_base_select_one_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>logarithm_base_select_one_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>natural</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Natural</t>
         </is>
       </c>
     </row>
